--- a/test/corpus/fixtures/threaded-comment-parts-survive-roundtrip/resolved-multi-author.xlsx
+++ b/test/corpus/fixtures/threaded-comment-parts-survive-roundtrip/resolved-multi-author.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\000023500\AppData\Local\Temp\claude\C--Users-000023500-dev-ts-xlsx\622c2b0e-7b34-4daf-8726-5eba7bde5173\scratchpad\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ts-xlsx\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{8D8552D6-73CC-40A2-A12F-95F24560B545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
